--- a/Q3/result1.xlsx
+++ b/Q3/result1.xlsx
@@ -528,98 +528,98 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>5.127459390641712</v>
+        <v>179.6487309709737</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>121.1625452683</v>
+        <v>139.9994359014</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17816.05824594434</v>
+        <v>17799.99448244593</v>
       </c>
       <c r="E2" t="n">
-        <v>1.44091792539092</v>
+        <v>3.382745049315239e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1800</v>
       </c>
       <c r="G2" t="n">
-        <v>17895.14767114484</v>
+        <v>17295.48227908764</v>
       </c>
       <c r="H2" t="n">
-        <v>8.53766877073811</v>
+        <v>3.093136560530286</v>
       </c>
       <c r="I2" t="n">
-        <v>1797.89535473585</v>
+        <v>1736.363954531199</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3907600403</v>
+        <v>3.851366071700967</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>5.127459390641712</v>
+        <v>179.6487309709737</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>121.1625452683</v>
+        <v>139.9994359014</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>17956.46727037566</v>
+        <v>17280.66640120076</v>
       </c>
       <c r="E3" t="n">
-        <v>14.03992038749321</v>
+        <v>3.18397089928329</v>
       </c>
       <c r="F3" t="n">
         <v>1800</v>
       </c>
       <c r="G3" t="n">
-        <v>17972.83066541486</v>
+        <v>16531.40309646653</v>
       </c>
       <c r="H3" t="n">
-        <v>15.50821956001537</v>
+        <v>7.777612758178012</v>
       </c>
       <c r="I3" t="n">
-        <v>1799.909907446117</v>
+        <v>1659.644718600327</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7920787811</v>
+        <v>2.579000649452613</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>5.127459390641712</v>
+        <v>179.6487309709737</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>121.1625452683</v>
+        <v>139.9994359014</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>18242.85317060801</v>
+        <v>17017.18748338021</v>
       </c>
       <c r="E4" t="n">
-        <v>39.73753260830463</v>
+        <v>4.799327981619096</v>
       </c>
       <c r="F4" t="n">
         <v>1800</v>
       </c>
       <c r="G4" t="n">
-        <v>18946.94792772357</v>
+        <v>16170.35116991101</v>
       </c>
       <c r="H4" t="n">
-        <v>102.9164601336574</v>
+        <v>9.991178046349013</v>
       </c>
       <c r="I4" t="n">
-        <v>1633.196834225467</v>
+        <v>1620.708880896909</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.189872364998052</v>
       </c>
     </row>
     <row r="5">

--- a/Q3/result1.xlsx
+++ b/Q3/result1.xlsx
@@ -528,98 +528,98 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>179.6487309709737</v>
+        <v>179.6487506585385</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>139.9994359014</v>
+        <v>139.9998317115418</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17799.99448244593</v>
+        <v>17799.99198046634</v>
       </c>
       <c r="E2" t="n">
-        <v>3.382745049315239e-05</v>
+        <v>4.916402619884366e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1800</v>
       </c>
       <c r="G2" t="n">
-        <v>17295.48227908764</v>
+        <v>17295.51900990325</v>
       </c>
       <c r="H2" t="n">
-        <v>3.093136560530286</v>
+        <v>3.092738015728472</v>
       </c>
       <c r="I2" t="n">
-        <v>1736.363954531199</v>
+        <v>1736.374211347738</v>
       </c>
       <c r="J2" t="n">
-        <v>3.851366071700967</v>
+        <v>3.852525167465132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>179.6487309709737</v>
+        <v>179.6487506585385</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>139.9994359014</v>
+        <v>139.9998317115418</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>17280.66640120076</v>
+        <v>17277.54542889506</v>
       </c>
       <c r="E3" t="n">
-        <v>3.18397089928329</v>
+        <v>3.202925670672898</v>
       </c>
       <c r="F3" t="n">
         <v>1800</v>
       </c>
       <c r="G3" t="n">
-        <v>16531.40309646653</v>
+        <v>16531.171120389</v>
       </c>
       <c r="H3" t="n">
-        <v>7.777612758178012</v>
+        <v>7.778598972925707</v>
       </c>
       <c r="I3" t="n">
-        <v>1659.644718600327</v>
+        <v>1660.725778872128</v>
       </c>
       <c r="J3" t="n">
-        <v>2.579000649452613</v>
+        <v>2.578173813820289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>179.6487309709737</v>
+        <v>179.6487506585385</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>139.9994359014</v>
+        <v>139.9998317115418</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>17017.18748338021</v>
+        <v>17017.55384967544</v>
       </c>
       <c r="E4" t="n">
-        <v>4.799327981619096</v>
+        <v>4.796812965945656</v>
       </c>
       <c r="F4" t="n">
         <v>1800</v>
       </c>
       <c r="G4" t="n">
-        <v>16170.35116991101</v>
+        <v>16170.22680104412</v>
       </c>
       <c r="H4" t="n">
-        <v>9.991178046349013</v>
+        <v>9.991380504664082</v>
       </c>
       <c r="I4" t="n">
-        <v>1620.708880896909</v>
+        <v>1620.502040746932</v>
       </c>
       <c r="J4" t="n">
-        <v>1.189872364998052</v>
+        <v>1.189492869377322</v>
       </c>
     </row>
     <row r="5">
